--- a/docs/testing/spreadsheet-output/platform-performance.xlsx
+++ b/docs/testing/spreadsheet-output/platform-performance.xlsx
@@ -29,10 +29,7 @@
     <t>Total Toko Aktif/Baru</t>
   </si>
   <si>
-    <t>31/12/2099</t>
-  </si>
-  <si>
-    <t>13/07/2026</t>
+    <t>01/01/2099</t>
   </si>
   <si>
     <t>12/07/2026</t>
@@ -53,6 +50,9 @@
     <t>07/07/2026</t>
   </si>
   <si>
+    <t>06/07/2026</t>
+  </si>
+  <si>
     <t>05/07/2026</t>
   </si>
   <si>
@@ -89,15 +89,15 @@
     <t>24/06/2026</t>
   </si>
   <si>
+    <t>23/06/2026</t>
+  </si>
+  <si>
     <t>22/06/2026</t>
   </si>
   <si>
     <t>21/06/2026</t>
   </si>
   <si>
-    <t>20/06/2026</t>
-  </si>
-  <si>
     <t>19/06/2026</t>
   </si>
   <si>
@@ -113,7 +113,7 @@
     <t>15/06/2026</t>
   </si>
   <si>
-    <t>13/06/2026</t>
+    <t>14/06/2026</t>
   </si>
 </sst>
 </file>
@@ -495,13 +495,13 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>214000.0</v>
+        <v>2327000.0</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -509,13 +509,13 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>1024000.0</v>
+        <v>2424000.0</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -523,13 +523,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>1249000.0</v>
+        <v>452000.0</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -537,13 +537,13 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>478000.0</v>
+        <v>765000.0</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -551,13 +551,13 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>641000.0</v>
+        <v>1811000.0</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -565,13 +565,13 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>2681000.0</v>
+        <v>230000.0</v>
       </c>
       <c r="C8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -579,13 +579,13 @@
         <v>11</v>
       </c>
       <c r="B9">
-        <v>598000.0</v>
+        <v>219000.0</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -593,13 +593,13 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>907000.0</v>
+        <v>778000.0</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -607,7 +607,7 @@
         <v>13</v>
       </c>
       <c r="B11">
-        <v>464000.0</v>
+        <v>46000.0</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -621,13 +621,13 @@
         <v>14</v>
       </c>
       <c r="B12">
-        <v>1828000.0</v>
+        <v>1027000.0</v>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -635,10 +635,10 @@
         <v>15</v>
       </c>
       <c r="B13">
-        <v>1064000.0</v>
+        <v>3311000.0</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -649,13 +649,13 @@
         <v>16</v>
       </c>
       <c r="B14">
-        <v>756000.0</v>
+        <v>655000.0</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -663,13 +663,13 @@
         <v>17</v>
       </c>
       <c r="B15">
-        <v>3506000.0</v>
+        <v>2985000.0</v>
       </c>
       <c r="C15">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -677,13 +677,13 @@
         <v>18</v>
       </c>
       <c r="B16">
-        <v>939000.0</v>
+        <v>1399000.0</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -691,13 +691,13 @@
         <v>19</v>
       </c>
       <c r="B17">
-        <v>184000.0</v>
+        <v>1084000.0</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -705,10 +705,10 @@
         <v>20</v>
       </c>
       <c r="B18">
-        <v>2106000.0</v>
+        <v>200000.0</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -719,7 +719,7 @@
         <v>21</v>
       </c>
       <c r="B19">
-        <v>1935000.0</v>
+        <v>2211000.0</v>
       </c>
       <c r="C19">
         <v>4</v>
@@ -733,13 +733,13 @@
         <v>22</v>
       </c>
       <c r="B20">
-        <v>1137000.0</v>
+        <v>150000.0</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -747,13 +747,13 @@
         <v>23</v>
       </c>
       <c r="B21">
-        <v>1038000.0</v>
+        <v>971000.0</v>
       </c>
       <c r="C21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -761,13 +761,13 @@
         <v>24</v>
       </c>
       <c r="B22">
-        <v>1805000.0</v>
+        <v>455000.0</v>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -775,10 +775,10 @@
         <v>25</v>
       </c>
       <c r="B23">
-        <v>2307000.0</v>
+        <v>1826000.0</v>
       </c>
       <c r="C23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D23">
         <v>2</v>
@@ -789,10 +789,10 @@
         <v>26</v>
       </c>
       <c r="B24">
-        <v>1366000.0</v>
+        <v>1196000.0</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24">
         <v>2</v>
@@ -803,13 +803,13 @@
         <v>27</v>
       </c>
       <c r="B25">
-        <v>1846000.0</v>
+        <v>1030000.0</v>
       </c>
       <c r="C25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D25">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -817,13 +817,13 @@
         <v>28</v>
       </c>
       <c r="B26">
-        <v>839000.0</v>
+        <v>149000.0</v>
       </c>
       <c r="C26">
         <v>2</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -831,10 +831,10 @@
         <v>29</v>
       </c>
       <c r="B27">
-        <v>2557000.0</v>
+        <v>1194000.0</v>
       </c>
       <c r="C27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D27">
         <v>3</v>
@@ -845,13 +845,13 @@
         <v>30</v>
       </c>
       <c r="B28">
-        <v>4052000.0</v>
+        <v>278000.0</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D28">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -859,7 +859,7 @@
         <v>31</v>
       </c>
       <c r="B29">
-        <v>1858000.0</v>
+        <v>1385000.0</v>
       </c>
       <c r="C29">
         <v>3</v>
@@ -873,13 +873,13 @@
         <v>32</v>
       </c>
       <c r="B30">
-        <v>1158000.0</v>
+        <v>324000.0</v>
       </c>
       <c r="C30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/testing/spreadsheet-output/platform-performance.xlsx
+++ b/docs/testing/spreadsheet-output/platform-performance.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="35">
   <si>
     <t>Tanggal</t>
   </si>
@@ -32,6 +32,21 @@
     <t>01/01/2099</t>
   </si>
   <si>
+    <t>17/07/2026</t>
+  </si>
+  <si>
+    <t>16/07/2026</t>
+  </si>
+  <si>
+    <t>15/07/2026</t>
+  </si>
+  <si>
+    <t>14/07/2026</t>
+  </si>
+  <si>
+    <t>13/07/2026</t>
+  </si>
+  <si>
     <t>12/07/2026</t>
   </si>
   <si>
@@ -80,9 +95,6 @@
     <t>27/06/2026</t>
   </si>
   <si>
-    <t>26/06/2026</t>
-  </si>
-  <si>
     <t>25/06/2026</t>
   </si>
   <si>
@@ -98,6 +110,9 @@
     <t>21/06/2026</t>
   </si>
   <si>
+    <t>20/06/2026</t>
+  </si>
+  <si>
     <t>19/06/2026</t>
   </si>
   <si>
@@ -105,15 +120,6 @@
   </si>
   <si>
     <t>17/06/2026</t>
-  </si>
-  <si>
-    <t>16/06/2026</t>
-  </si>
-  <si>
-    <t>15/06/2026</t>
-  </si>
-  <si>
-    <t>14/06/2026</t>
   </si>
 </sst>
 </file>
@@ -453,7 +459,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="12.854" bestFit="true" customWidth="true" style="0"/>
@@ -484,7 +490,7 @@
         <v>5000000.0</v>
       </c>
       <c r="C2">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D2">
         <v>25</v>
@@ -495,10 +501,10 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>2327000.0</v>
+        <v>979000.0</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -509,13 +515,13 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>2424000.0</v>
+        <v>1210000.0</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -523,13 +529,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>452000.0</v>
+        <v>232000.0</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -537,13 +543,13 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>765000.0</v>
+        <v>1145000.0</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -551,13 +557,13 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>1811000.0</v>
+        <v>2229000.0</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -565,10 +571,10 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>230000.0</v>
+        <v>697000.0</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -579,13 +585,13 @@
         <v>11</v>
       </c>
       <c r="B9">
-        <v>219000.0</v>
+        <v>475000.0</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -593,13 +599,13 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>778000.0</v>
+        <v>2737000.0</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -607,7 +613,7 @@
         <v>13</v>
       </c>
       <c r="B11">
-        <v>46000.0</v>
+        <v>921000.0</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -621,7 +627,7 @@
         <v>14</v>
       </c>
       <c r="B12">
-        <v>1027000.0</v>
+        <v>1129000.0</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -635,10 +641,10 @@
         <v>15</v>
       </c>
       <c r="B13">
-        <v>3311000.0</v>
+        <v>2686000.0</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -649,10 +655,10 @@
         <v>16</v>
       </c>
       <c r="B14">
-        <v>655000.0</v>
+        <v>504000.0</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -663,13 +669,13 @@
         <v>17</v>
       </c>
       <c r="B15">
-        <v>2985000.0</v>
+        <v>790000.0</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D15">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -677,13 +683,13 @@
         <v>18</v>
       </c>
       <c r="B16">
-        <v>1399000.0</v>
+        <v>1401000.0</v>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -691,13 +697,13 @@
         <v>19</v>
       </c>
       <c r="B17">
-        <v>1084000.0</v>
+        <v>1511000.0</v>
       </c>
       <c r="C17">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -705,13 +711,13 @@
         <v>20</v>
       </c>
       <c r="B18">
-        <v>200000.0</v>
+        <v>1478000.0</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -719,13 +725,13 @@
         <v>21</v>
       </c>
       <c r="B19">
-        <v>2211000.0</v>
+        <v>397000.0</v>
       </c>
       <c r="C19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D19">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -733,13 +739,13 @@
         <v>22</v>
       </c>
       <c r="B20">
-        <v>150000.0</v>
+        <v>722000.0</v>
       </c>
       <c r="C20">
         <v>2</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -747,13 +753,13 @@
         <v>23</v>
       </c>
       <c r="B21">
-        <v>971000.0</v>
+        <v>278000.0</v>
       </c>
       <c r="C21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D21">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -761,13 +767,13 @@
         <v>24</v>
       </c>
       <c r="B22">
-        <v>455000.0</v>
+        <v>1686000.0</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -775,13 +781,13 @@
         <v>25</v>
       </c>
       <c r="B23">
-        <v>1826000.0</v>
+        <v>1839000.0</v>
       </c>
       <c r="C23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -789,7 +795,7 @@
         <v>26</v>
       </c>
       <c r="B24">
-        <v>1196000.0</v>
+        <v>2476000.0</v>
       </c>
       <c r="C24">
         <v>3</v>
@@ -803,13 +809,13 @@
         <v>27</v>
       </c>
       <c r="B25">
-        <v>1030000.0</v>
+        <v>2324000.0</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -817,7 +823,7 @@
         <v>28</v>
       </c>
       <c r="B26">
-        <v>149000.0</v>
+        <v>2022000.0</v>
       </c>
       <c r="C26">
         <v>2</v>
@@ -831,13 +837,13 @@
         <v>29</v>
       </c>
       <c r="B27">
-        <v>1194000.0</v>
+        <v>497000.0</v>
       </c>
       <c r="C27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D27">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -845,7 +851,7 @@
         <v>30</v>
       </c>
       <c r="B28">
-        <v>278000.0</v>
+        <v>337000.0</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -859,13 +865,13 @@
         <v>31</v>
       </c>
       <c r="B29">
-        <v>1385000.0</v>
+        <v>999000.0</v>
       </c>
       <c r="C29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -873,12 +879,40 @@
         <v>32</v>
       </c>
       <c r="B30">
-        <v>324000.0</v>
+        <v>210000.0</v>
       </c>
       <c r="C30">
         <v>1</v>
       </c>
       <c r="D30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31">
+        <v>2928000.0</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32">
+        <v>179000.0</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
         <v>1</v>
       </c>
     </row>
